--- a/data/trans_camb/P32C-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,0</t>
+          <t>-0,6; 3,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,98</t>
+          <t>-2,12; 0,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,32</t>
+          <t>-2,66; 0,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,0</t>
+          <t>-3,66; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,0</t>
+          <t>-4,56; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,46</t>
+          <t>-2,3; 1,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,32</t>
+          <t>-0,96; 2,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,25</t>
+          <t>-1,88; 0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,33</t>
+          <t>-1,83; 0,39</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 1155,25</t>
+          <t>-50,33; 903,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,19; 436,3</t>
+          <t>-62,34; 581,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 147,89</t>
+          <t>-100,0; 192,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,1</t>
+          <t>-1,05; 4,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,17</t>
+          <t>-1,41; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,64</t>
+          <t>-2,24; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,0</t>
+          <t>-3,1; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,0</t>
+          <t>-3,38; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,0</t>
+          <t>-3,38; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,69</t>
+          <t>-1,04; 2,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,39</t>
+          <t>-1,31; 1,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,81</t>
+          <t>-1,75; 0,86</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,08</t>
+          <t>-2,31; 0,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,69</t>
+          <t>-2,14; 1,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,43</t>
+          <t>-2,15; 1,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,79</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,97</t>
+          <t>-1,91; 0,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,69</t>
+          <t>-1,58; 1,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,21</t>
+          <t>-1,82; 1,11</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-86,62; 195,46</t>
+          <t>-90,7; 191,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 256,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 294,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-86,68; 278,95</t>
+          <t>-87,99; 211,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,23; 303,37</t>
+          <t>-82,79; 311,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 321,34</t>
+          <t>-100,0; 201,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,96</t>
+          <t>-2,13; 1,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,9</t>
+          <t>-2,17; 1,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,25</t>
+          <t>-2,87; 0,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,88</t>
+          <t>-3,04; 0,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,36</t>
+          <t>-2,64; 1,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,83</t>
+          <t>-2,78; 0,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,66</t>
+          <t>-1,87; 0,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,71</t>
+          <t>-1,9; 0,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; -0,11</t>
+          <t>-2,64; -0,13</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,92; 62,76</t>
+          <t>-62,92; 74,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,5; 60,89</t>
+          <t>-67,01; 77,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,19; 37,22</t>
+          <t>-82,63; 31,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 56,05</t>
+          <t>-65,84; 48,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,75; 54,98</t>
+          <t>-64,38; 56,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-85,74; -2,85</t>
+          <t>-86,67; -7,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,97</t>
+          <t>-3,08; 2,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,88</t>
+          <t>-4,01; 1,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,21</t>
+          <t>-2,97; 3,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 0,56</t>
+          <t>-5,62; 0,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,0</t>
+          <t>-6,61; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,11</t>
+          <t>-4,54; 1,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 1,22</t>
+          <t>-2,87; 1,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,65</t>
+          <t>-3,41; 0,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,99</t>
+          <t>-2,44; 1,86</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,45; 201,23</t>
+          <t>-66,98; 191,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-79,05; 148,83</t>
+          <t>-79,91; 124,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 221,44</t>
+          <t>-67,74; 285,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,37; 92,23</t>
+          <t>-69,27; 101,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-83,08; 55,15</t>
+          <t>-82,2; 60,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-63,01; 152,48</t>
+          <t>-61,7; 126,91</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,86</t>
+          <t>-1,49; 3,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,41</t>
+          <t>-1,64; 2,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,0</t>
+          <t>-3,75; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1777,27 +1777,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,04</t>
+          <t>-1,59; 2,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 7,96</t>
+          <t>-1,4; 7,34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,93</t>
+          <t>-1,64; 1,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,87</t>
+          <t>-1,02; 1,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,26</t>
+          <t>-1,15; 3,85</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-78,39; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,05</t>
+          <t>-0,83; 0,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,64</t>
+          <t>-1,28; 0,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,11</t>
+          <t>-1,57; 0,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,04</t>
+          <t>-1,48; 0,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,37</t>
+          <t>-1,37; 0,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,83</t>
+          <t>-1,1; 0,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,53</t>
+          <t>-0,77; 0,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,3</t>
+          <t>-1,02; 0,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,07</t>
+          <t>-1,19; 0,03</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 71,0</t>
+          <t>-34,18; 65,28</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 47,6</t>
+          <t>-51,77; 36,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 12,2</t>
+          <t>-64,05; 5,34</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,18</t>
+          <t>-100,0; 73,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-82,51; 111,55</t>
+          <t>-85,58; 122,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,04; 197,2</t>
+          <t>-74,99; 218,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 44,65</t>
+          <t>-41,38; 39,81</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-50,01; 26,39</t>
+          <t>-52,7; 23,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-61,68; 7,32</t>
+          <t>-59,84; 3,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32C-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,63</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,98</t>
+          <t>-0,6; 4,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,77</t>
+          <t>-2,22; 0,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,02</t>
+          <t>-2,64; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,0</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,0</t>
+          <t>-4,86; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,66</t>
+          <t>-2,61; 1,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,31</t>
+          <t>-0,82; 2,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,45</t>
+          <t>-1,94; 0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,39</t>
+          <t>-2,09; 0,26</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-74,84%</t>
+          <t>-76,98%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-55,12%</t>
+          <t>-57,61%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,33; 903,0</t>
+          <t>-49,29; 1042,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 581,52</t>
+          <t>-61,33; 750,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 192,62</t>
+          <t>-100,0; 114,52</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,12</t>
+          <t>-1,17; 4,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,12</t>
+          <t>-1,51; 2,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,56</t>
+          <t>-2,17; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,0</t>
+          <t>-3,86; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,0</t>
+          <t>-3,4; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,0</t>
+          <t>-3,86; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,48</t>
+          <t>-0,99; 2,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,53</t>
+          <t>-1,46; 1,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,86</t>
+          <t>-2,0; 0,96</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-28,11%</t>
+          <t>-6,6%</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,43</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,96</t>
+          <t>-2,29; 1,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,51</t>
+          <t>-2,05; 1,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,28</t>
+          <t>-2,22; 1,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 11,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,9</t>
+          <t>-1,82; 0,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,78</t>
+          <t>-1,68; 1,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,11</t>
+          <t>-1,83; 1,0</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-26,16%</t>
+          <t>-31,08%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-26,69%</t>
+          <t>-32,33%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-90,7; 191,54</t>
+          <t>-88,05; 230,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 256,41</t>
+          <t>-100,0; 351,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 196,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,99; 211,73</t>
+          <t>-88,29; 198,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,79; 311,33</t>
+          <t>-100,0; 241,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 201,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-0,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,06</t>
+          <t>-2,2; 1,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,06</t>
+          <t>-2,17; 1,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 0,27</t>
+          <t>-2,92; 0,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,88</t>
+          <t>-3,02; 0,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,08</t>
+          <t>-2,65; 1,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,92</t>
+          <t>-1,28; 4,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,68</t>
+          <t>-1,95; 0,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,71</t>
+          <t>-2,03; 0,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,13</t>
+          <t>-2,04; 0,55</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-50,26%</t>
+          <t>-51,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-35,22%</t>
+          <t>139,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-57,18%</t>
+          <t>-34,2%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 74,98</t>
+          <t>-61,19; 82,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-67,01; 77,08</t>
+          <t>-66,05; 73,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,63; 31,76</t>
+          <t>-82,48; 17,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,84; 48,12</t>
+          <t>-64,87; 54,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,38; 56,32</t>
+          <t>-67,75; 47,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-86,67; -7,79</t>
+          <t>-71,96; 58,57</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,74</t>
+          <t>-3,03; 2,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,79</t>
+          <t>-3,64; 1,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,13</t>
+          <t>-3,31; 2,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,55</t>
+          <t>-5,56; 0,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 0,0</t>
+          <t>-6,64; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1,99</t>
+          <t>-5,06; 1,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,46</t>
+          <t>-2,86; 1,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,68</t>
+          <t>-3,42; 0,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,86</t>
+          <t>-2,62; 1,63</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>-7,51%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-16,85%</t>
+          <t>-25,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,72%</t>
+          <t>-11,58%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 191,4</t>
+          <t>-64,0; 185,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-79,91; 124,7</t>
+          <t>-78,49; 144,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 285,77</t>
+          <t>-67,65; 191,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1672,29 +1672,29 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,27; 101,83</t>
+          <t>-68,82; 105,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-82,2; 60,83</t>
+          <t>-80,63; 73,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,7; 126,91</t>
+          <t>-64,54; 112,94</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,71</t>
+          <t>-1,49; 3,69</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,45</t>
+          <t>-1,63; 2,86</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,0</t>
+          <t>-3,81; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,4</t>
+          <t>-2,81; 0,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,04</t>
+          <t>-1,52; 2,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 7,34</t>
+          <t>-1,4; 7,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,06</t>
+          <t>-1,68; 0,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,73</t>
+          <t>-1,19; 1,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,85</t>
+          <t>-1,15; 4,41</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,14; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,39</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,95</t>
+          <t>-0,74; 1,12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,5</t>
+          <t>-1,15; 0,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,03</t>
+          <t>-1,46; 0,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,06</t>
+          <t>-1,46; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,38</t>
+          <t>-1,4; 0,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,83</t>
+          <t>-0,71; 1,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,47</t>
+          <t>-0,8; 0,45</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,3</t>
+          <t>-1,04; 0,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,03</t>
+          <t>-1,02; 0,25</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-35,14%</t>
+          <t>-35,61%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-16,73%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-33,75%</t>
+          <t>-24,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 65,28</t>
+          <t>-31,72; 81,28</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 36,42</t>
+          <t>-49,74; 45,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,05; 5,34</t>
+          <t>-62,81; 6,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,05</t>
+          <t>-100,0; 30,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-85,58; 122,32</t>
+          <t>-86,41; 90,44</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-74,99; 218,96</t>
+          <t>-56,61; 314,23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 39,81</t>
+          <t>-42,26; 36,67</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-52,7; 23,51</t>
+          <t>-51,78; 20,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-59,84; 3,83</t>
+          <t>-54,45; 21,19</t>
         </is>
       </c>
     </row>
